--- a/important_mails_2026-07-04.xlsx
+++ b/important_mails_2026-07-04.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6227,7 +6227,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -6242,74 +6242,22 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Thu, 4 Jun 2026 15:15:46 +0000</t>
+          <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
+ B0DD7R3PPG</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 06/04/26 15:15 BST, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
- 316.41.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To find out more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
- B0DD7R3PPG</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6321,40 +6269,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:52:15 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -6373,39 +6321,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 12:40:58 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6421,39 +6369,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:56:40 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6479,39 +6427,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:39:22 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6537,39 +6485,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:15:17 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -6578,39 +6526,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 04:34:37 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -6635,40 +6583,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 06:03:25 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -6686,40 +6634,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 19:23:07 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6744,39 +6692,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:11:59 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -6795,39 +6743,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:32 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6846,39 +6794,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:28 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -6897,39 +6845,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:32:14 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"pars-rp-core-sellerappeals-transfer@amazon.com" &lt;pars-rp-core-sellerappeals-transfer@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20516062511] 危险物品（危险品）</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20516062511] 危险物品（危险品）
@@ -6957,39 +6905,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:22 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7008,39 +6956,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Important message: your account is at risk of deactivation</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  96
@@ -7060,40 +7008,40 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 06:46:26 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7109,40 +7057,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 10:18:49 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7169,39 +7117,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 03:03:53 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Review issue on FBA Shipment (FBA1234567)</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Review shipment defects to avoid reoccurrence
@@ -7221,40 +7169,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 13:54:53 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7267,40 +7215,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 10:51:40 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7319,39 +7267,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 13:08:16 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -7370,40 +7318,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 04:06:26 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -7419,39 +7367,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:04:36 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>New EU restriction on textile and footwear disposal</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  By July 19, update your removal settings for apparel, clothing and footwear in EU fulfillment centers
@@ -7466,39 +7414,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:11:21 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7516,40 +7464,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:29:01 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7561,39 +7509,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 18:10:54 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7611,39 +7559,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 15:30:18 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.es sales</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tu factura con IVA de los cargos del servicio RAP - Pagamos en tu nombre para las ventas de Amazon.es |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.es sales
@@ -7656,40 +7604,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 08:56:37 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7705,40 +7653,40 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 08:52:27 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GKPTF1T7, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GKPTF1T7, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -7766,39 +7714,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 17:51:49 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -7817,39 +7765,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 19:25:12 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7867,39 +7815,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 03:06:03 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -7919,39 +7867,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:23:36 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7969,39 +7917,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:17:04 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8019,288 +7967,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:40:15 +0000</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>Submit product compliance documents to avoid listing removal</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product compliance documents to avoid listing removal
- Hello Weihai EU,
- Your listings are at risk of removal due to missing Safety Data Sheets. Submit the required documentation by 2026-09-01 to continue selling these products. You can find examples of your at-risk listings at the bottom of this email.
- Why is this happening?
- We are taking this action because we identified hazardous products in your catalog that require Safety Data Sheets (SDS). These documents are required by law and provide critical safety information about chemical products, including proper handling, storage, and emergency procedures. This helps ensure the safety of our customers, employees, and anyone who handles these products.
- We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- To learn more, visit our Requirements and FAQ for the sale of chemicals .
- How do I continue to sell the affected products?
- To avoid listing removal and continue selling these products, upload the Safety Data Sheets (SDS) for each of the impacted products. Click the “View Compliance Requirements” button below to see all affected listings.
- View Compliance</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:33:38 +0000</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>Submit product compliance documents to avoid listing removal</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product compliance documents to avoid listing removal
- Hello Weihai EU,
- Your listings are at risk of removal due to missing Safety Data Sheets. Submit the required documentation by 2026-09-01 to continue selling these products. You can find examples of your at-risk listings at the bottom of this email.
- Why is this happening?
- We are taking this action because we identified hazardous products in your catalogue that require Safety Data Sheets (SDS). These documents are required by law and provide critical safety information about chemical products, including proper handling, storage and emergency procedures. This helps ensure the safety of our customers, employees and anyone who handles these products.
- To learn more, go to our Requirements and FAQ for the sale of chemicals .
- How do I continue to sell the affected products?
- To avoid listing removal and continue selling these products, upload the Safety Data Sheets (SDS) for each of the affected products. Click the “View Compliance Requirements” button below to see all affected listings.
- View Compliance Requirements
- What was affected?
- Reason
- At-risk sales
- Roaxkois Ceramic Painting Set | Cups Painting Set Includes C</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 21:10:43 +0000</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:18:22 +0000</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:12:35 +0000</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8315,39 +8014,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -8375,39 +8074,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para julio</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para julio
@@ -8436,39 +8135,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:42 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Łącze do zaktualizowanego raportu podatkowego dotyczącego Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Ponownie przesyłamy kwartalny raport podatkowy, który obejmuje dane takie jak informacje o tożsamości, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -8486,39 +8185,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 10:01:00 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8537,39 +8236,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:26 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -8583,39 +8282,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 00:26:49 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;
@@ -8630,39 +8329,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09:29:52 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Prime会员日明天开始：最后提报促销活动的机会</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -8686,39 +8385,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8733,39 +8432,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 10:18:43 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8786,39 +8485,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 10:02:13 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>最后机会：请于6月19日前提报 Prime Day 促销</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -8841,39 +8540,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:18:31 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -8893,39 +8592,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:14:39 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Soumettre les numéros d'enregistrement REP avant le 30 juin</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -8934,39 +8633,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 09:11:12 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -8986,40 +8685,40 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:13:19 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Get increased New Selection Program (2026) benefits starting July
  30</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
@@ -9033,39 +8732,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 00:29:05 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;
@@ -9081,39 +8780,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:26:46 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9128,39 +8827,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:13:30 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -9177,39 +8876,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:43 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -9227,40 +8926,40 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:12 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -9278,39 +8977,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:08:19 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -9328,39 +9027,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:17:27 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -9399,39 +9098,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:32 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -9449,39 +9148,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:13 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, xiao jianming:
@@ -9499,40 +9198,40 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:15:21 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -9550,39 +9249,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:24 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Documents de sécurité des produits requis pour les garder actifs</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour xiao jianming,
@@ -9600,39 +9299,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:34:40 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -9647,39 +9346,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 17:10:30 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -9697,40 +9396,40 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 04:55:50 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Hemos actualizado los requisitos del distintivo de Prime para Prime
  Day</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
  Para ayudarte a mantener el distintivo de Prime durante Prime Day, hemos actualizado nuestros requisitos del distintivo en España.
@@ -9751,39 +9450,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:49:02 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -9805,39 +9504,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:44:43 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -9857,39 +9556,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:35:25 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut des matières dangereuses (Hazmat)</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut des matières dangereuses (Hazmat)
@@ -9901,39 +9600,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:03:25 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -9945,39 +9644,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:03:17 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -9999,39 +9698,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:41:38 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>"Pereira, Sheryl" &lt;persher@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Amazon India your next growth market</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>Hi Team,
 Sheryl this side from Amazon India Out of Country team, we work with high-potential global brands to successfully launch and scale their presence in India. Given the current selection gaps and growing customer demand, I believe Amazon.in could be a great opportunity for Roaxkois
@@ -10045,39 +9744,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 08:25:43 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -10105,39 +9804,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:16:28 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>27 lipca rozpocznie się ulepszanie tytułów stron produktów</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>96
  Tytuły we wszystkich kategoriach (z wyjątkiem kategorii „Media”) będą musiały zawierać 75 znaków lub mniej, łącznie ze spacjami. Nowa funkcja „Najważniejsze informacje” zapewnia dodatkowe 125 znaków, umożliwiając udostępnianie materiałów.
@@ -10148,40 +9847,40 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:08:24 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti per migliorare i titoli dei prodotti a partire dal 27
  luglio</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>96
  I titoli in tutte le categorie eccetto i prodotti multimediali dovranno contenere un massimo di 75 caratteri, spazi inclusi. Nelle caratteristiche principali dei prodotti, saranno ora disponibili altri 125 caratteri per descrivere i materiali.
@@ -10192,39 +9891,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:05:34 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Updates om je producttitels te verbeteren beginnen op 27 juli</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>96
  Titels in alle categorieën, behalve in de categorie ‘media’ mogen maximaal 75 tekens lang zijn, inclusief spaties. Met de nieuwe functie Itemhoogtepunten kun je nu 125 extra tekens gebruiken om materiaal te delen.
@@ -10236,39 +9935,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:05:16 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Las actualizaciones para mejorar los títulos de los productos entrarán en vigor el 27 de julio</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Los títulos de todas las categorías, excepto multimedia, tendrán que tener 75 caracteres o menos, contando espacios. La nueva herramienta de aspectos destacados del producto ahora ofrece 125 caracteres más para compartir materiales.
@@ -10279,39 +9978,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:10:59 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Nueva restricción de la UE sobre la puesta de inventario de productos textiles y calzado a disposición de Amazon</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>96
  A más tardar el 19 de julio, actualiza la configuración de retiradas de prendas de vestir y calzado en los centros logísticos de la UE
@@ -10324,40 +10023,40 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:03:48 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Nuove limitazioni dell'Unione europea sul reimpiego di prodotti
  tessili e calzature</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorna le impostazioni di rimozione per capi di abbigliamento, accessori e calzature nei centri logistici dell'Unione europea entro il 19 luglio
@@ -10370,39 +10069,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:26:32 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Nowe ograniczenia UE dotyczące usuwania tekstyliów i obuwia</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Do 19 lipca zmień ustawienia wycofywania zapasów odzieży i obuwia magazynowanych w centrach logistycznych w UE
@@ -10416,39 +10115,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:08:34 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Nouvelle restriction de l’UE sur la mise au rebut des textiles et des chaussures</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>96
  D’ici le 19 juillet, mettez à jour vos paramètres de demande de prélèvement pour les vêtements, les accessoires vestimentaires et les chaussures dans les centres de distribution de l’UE
@@ -10461,39 +10160,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 15:18:50 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -10515,39 +10214,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:50:24 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Statusuppdatering för farligt gods</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>96
  Statusuppdatering för farligt gods
@@ -10569,39 +10268,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:16:55 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -10622,39 +10321,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:10:30 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -10675,39 +10374,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:05:17 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -10729,39 +10428,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:05:00 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -10783,39 +10482,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 19:32:37 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 5/2026
  96
@@ -10838,39 +10537,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 08:39:32 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026
  96
@@ -10894,39 +10593,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 07:48:24 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -10953,39 +10652,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:51:17 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 5/2026</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 5/2026
  96
@@ -11012,39 +10711,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:47:21 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 5/2026
  96
@@ -11064,39 +10763,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:42:19 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 5/2026</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 5/2026
  96
@@ -11123,39 +10822,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:15:01 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 5/2026</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Verkäufer for 5/2026
  96
@@ -11179,39 +10878,39 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:12:39 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Korygująca Sprzedawcy for 5/2026</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Korygująca Sprzedawcy for 5/2026
  96
@@ -11235,39 +10934,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:57:10 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 5/2026</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 5/2026
  96
@@ -11285,39 +10984,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:54:32 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 5/2026
  96
@@ -11341,39 +11040,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:42:06 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 5/2026
  96
@@ -11396,39 +11095,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:59 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -11443,39 +11142,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:01:19 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -11493,39 +11192,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 12:36:48 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -11552,39 +11251,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 12:31:12 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -11611,39 +11310,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:43:20 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -11668,39 +11367,39 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:38:16 +0000</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -11725,39 +11424,39 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:25:17 +0000</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -11784,39 +11483,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:21:01 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -11841,39 +11540,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:10:07 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -11900,39 +11599,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 10:55:24 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026
  96
@@ -11951,39 +11650,39 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 10:25:16 +0000</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026
  96
@@ -12002,39 +11701,39 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 09:33:20 +0000</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -12058,39 +11757,39 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 07:52:40 +0000</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 5/2026
  96
@@ -12114,39 +11813,39 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 07:36:30 +0000</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -12173,39 +11872,39 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:48:36 +0000</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -12229,39 +11928,39 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:24:07 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 5/2026</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 5/2026
  96
@@ -12286,39 +11985,39 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:01:50 +0000</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 5/2026
  96
@@ -12343,39 +12042,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:56:14 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 5/2026
  96
@@ -12393,39 +12092,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:28:55 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 5/2026</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 5/2026
  96
@@ -12452,39 +12151,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:23:44 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 5/2026
  96
@@ -12502,39 +12201,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:10:53 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 5/2026</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 5/2026
  96
@@ -12559,39 +12258,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:02:43 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 5/2026</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 5/2026
  96
@@ -12618,39 +12317,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 04:45:31 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 5/2026
  96
@@ -12671,39 +12370,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 13:05:07 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -12733,39 +12432,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:43:35 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -12790,39 +12489,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:33:36 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -12849,39 +12548,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:16:55 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -12899,39 +12598,39 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:09:15 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -12949,39 +12648,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:09:08 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -13005,39 +12704,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 11:58:55 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -13062,39 +12761,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 11:38:44 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -13121,40 +12820,40 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 23:11:17 +0000</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -13170,40 +12869,40 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 23:10:46 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -13219,39 +12918,39 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:37:38 +0000</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -13290,39 +12989,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:31:54 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -13338,39 +13037,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:14:06 +0000</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -13386,39 +13085,39 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:10:02 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -13434,679 +13133,39 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:43:42 +0000</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>Presenta documentos de cumplimiento normativo del producto para
- evitar que se retiren los listings</t>
-        </is>
-      </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
-        <is>
-          <t>96
- Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
- Hola, Weihai EU:
- Tus listings están en riesgo de retirada porque faltan fichas de datos de seguridad (FDS). Presenta la documentación necesaria a más tardar el 2026-09-01 para seguir vendiendo estos productos. Encontrarás ejemplos de los listings en riesgo al final de este correo electrónico.
- ¿A qué se debe esto?
- Hemos tomado esta medida porque hemos identificado que hay productos peligrosos en tu catálogo que requieren fichas de datos de seguridad (FDS). Estos documentos son obligatorios por ley y proporcionan información importante sobre la seguridad de los productos químicos, como los procedimientos adecuados de manipulación, almacenamiento y emergencia. Así podemos garantizar la seguridad de nuestros clientes, empleados y cualquier persona que se encargue de estos productos.
- Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar esta decisión.
- Para más información, consulta Requisitos y preguntas frecuentes para la venta de productos químicos .
- ¿Cómo puedo seguir vendiendo los productos afectados?
- Para evita</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:42:40 +0000</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>Documenten over productconformiteit indienen om verwijdering van
- productvermeldingen te voorkomen</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>96
- Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
- Hallo Weihai EU,
- Je productvermeldingen lopen het risico te worden verwijderd vanwege ontbrekende veiligheidsinformatiebladen. Dien de vereiste documentatie uiterlijk 2026-09-01 in om door te gaan met het verkopen van deze producten. Onderaan deze e-mail vind je voorbeelden van je productvermeldingen met een verhoogd risico.
- Waarom gebeurt dit?
- We ondernemen deze actie omdat we gevaarlijke producten in je catalogus hebben geïdentificeerd waarvoor veiligheidsinformatiebladen (SDS) nodig zijn. Deze documenten zijn wettelijk vereist en bieden kritieke veiligheidsinformatie over chemische producten, inclusief correcte verwerking, opslag en noodprocedures. Dit helpt de veiligheid te waarborgen van onze klanten, medewerkers en iedereen die met deze producten omgaat.
- We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
- Ga voor meer informatie naar onze Vereisten en veelgestelde vragen voor de verkoop van chemische stoffen .
- Hoe kan ik de getroffen producten blijve</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:38:41 +0000</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
-        </is>
-      </c>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
- Dzień dobry Weihai EU,
- Twoje oferty mogą zostać usunięte z powodu braku kart charakterystyki. Aby móc dalej sprzedawać te produkty, prześlij wymaganą dokumentację do 2026-09-01. Przykłady zagrożonych ofert znajdziesz na dole tej wiadomości e-mail.
- Dlaczego tak się stało?
- Podejmujemy te działania, ponieważ stwierdziliśmy, że w Twoim katalogu znajdują się produkty niebezpieczne, dla których wymagane są karty charakterystyki. Dokumenty te są wymagane przepisami prawa i zawierają istotne informacje związane z bezpieczeństwem produktów chemicznych, w tym dotyczące prawidłowego obchodzenia się z nimi, przechowywania ich oraz postępowania w nagłych wypadkach. Pomaga to zapewnić bezpieczeństwo naszym klientom, pracownikom i każdej osobie mającej styczność z tymi produktami.
- Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
- Więcej informacji znajdziesz na stronie Wymagania i często zadawane pytania dotyczące sprzedaży chemikaliów .
- Co mogę zrobić, aby dalej sprzedawać produkty, których dotyczy </t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:37:16 +0000</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F256" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
-        </is>
-      </c>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr">
-        <is>
-          <t>96
- Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
- Hej Weihai EU!
- Dina annonser riskerar att tas bort på grund av att säkerhetsdatablad saknas. Skicka in den dokumentation som krävs senast 2026-09-01 för att fortsätta sälja dessa produkter. Vid slutet av det här e-postmeddelandet kan du se exempel på dina produktposter i riskzonen.
- Varför händer det här?
- Vi vidtar denna åtgärd eftersom vi identifierade farliga produkter som kräver säkerhetsdatablad (SDS) i din katalog. Dessa dokument är obligatoriska enligt lag och tillhandahåller viktig säkerhetsinformation om kemiska produkter, inklusive korrekt hantering, lagring och nödrutiner. Detta bidrar till att säkerställa säkerheten för våra kunder, anställda och alla som hanterar dessa produkter.
- Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
- Du hittar mer information i Krav och Vanliga frågor för försäljning av kemikalier .
- Hur fortsätter jag att sälja de berörda produkterna?
- För att fortsätta sälja dessa produkter och undvika att produktposterna tas bort ska du ladda upp säkerhetsdatablad för var o</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:35:16 +0000</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F257" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
-        </is>
-      </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
- Gentile Weihai EU,
- Le tue offerte sono a rischio di rimozione a causa della mancanza delle schede di dati di sicurezza. Invia la documentazione richiesta entro il 2026-09-01 per continuare a vendere questi prodotti. In fondo a questa e-mail, puoi trovare alcuni esempi di offerte a rischio.
- Ciò a cosa è dovuto?
- Stiamo intraprendendo questa azione perché abbiamo identificato nel tuo catalogo dei prodotti pericolosi che richiedono schede di dati di sicurezza (SDS). Questi documenti sono obbligatori per legge e forniscono informazioni essenziali sulla sicurezza dei prodotti chimici, incluse indicazioni per la manipolazione, lo stoccaggio e le procedure di emergenza appropriate. Ciò contribuisce a garantire la sicurezza dei nostri clienti, dipendenti e di chiunque manipoli questi prodotti.
- Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- Per maggiori informazioni, consulta la pagina Requisiti e domande frequenti per la vendita di sostanze chimiche .
- Come faccio a continuare a v</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:31:58 +0000</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
-        </is>
-      </c>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
- Bonjour Weihai EU,
- Vos mises en vente risquent d’être supprimées en raison de l’absence de fiches de sécurité. Soumettez les documents requis avant le 2026-09-01 pour continuer à vendre ces produits. Vous trouverez des exemples de vos mises en vente à risque en bas de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure car nous avons identifié des produits dangereux dans votre catalogue qui nécessitent des fiches de sécurité. Ces documents sont requis par la loi et fournissent des informations essentielles de sécurité sur les produits chimiques, y compris les procédures de manipulation, de stockage et d’urgence appropriées. Cela permet d’assurer la sécurité de nos clients, de nos employés et de toute personne manipulant ces produits.
- Nous avons utilisé une combinaison de moyens automatisés et de contrôles par des experts humains pour identifier ce problème et prendre cette décision.
- Pour en savoir plus, consultez nos Exigences et FAQ pour la mise en vente de produits chimiques .
- Comment continuer à vendre les produits concernés ?
- Pour éviter le retrait d’une mis</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:35:34 +0000</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F259" s="2" t="inlineStr">
-        <is>
-          <t>提交商品安全文件以重新启售商品</t>
-        </is>
-      </c>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="inlineStr">
-        <is>
-          <t>96
- 提交商品安全文件以重新启售商品
- 尊敬的 Weihai EU：
-您好！
- 您的部分商品因缺少必要的商品合规信息而被停售。查看下面的详细信息和后续步骤。受影响的商品显示在此电子邮件的末尾。
- 为什么会发生这种情况？
- 我们之所以采取此措施，是因为这些商品缺少必要的合规信息。请查看我们的 商品安全与合规 帮助页面，了解有关适用法律法规和亚马逊政策的信息。为了确定此问题，我们综合运用了自动化技术和专家人工评审，最终做出这一决定。
- 此电子邮件末尾的表格提供了特定于商品的合规性要求。
- 如何重新启售商品？
- 要提供所需的合规信息，请前往 账户状况 页面并找到商品合规性请求：
--
- 如果您有所需的文件，请按照相关说明提交您的合规文件。我们仅会重新启售满足合规要求的商品。
--
- 如果您认为您的商品无需遵守这些要求，请提交相关文件，说明它们为何不受这些合规要求的约束。
- 有关分步操作说明，请参阅 提交合规文件或对文件请求提出申诉 帮助页面。
- 为避免进一步影响您的账户，请停售或删除您不打算销售或申诉的任何不合规商品。
- 如果我未执行上述操作，会怎么样？
- 如果您未提供所需的合规信息，则受影响的 ASIN 将一直处于停售状态，直到您或其他发布此商品的销售伙伴满足合规要求。
- 这些商品的亚马逊物流库存会怎样？
- 您必须在收到本通知后的 30 天内从我们的运营中心移除这些商品。如果未移除，我们将按照《亚马逊服务商业解决方案协议》中的规定弃置此库存，并且费用由您承担。要了解如何移除库存，请参阅 移除库存 帮助页面。
- 我们愿意随时为您提供帮助。
- 有关更多信息，请观看卖家大学中的 安全与合规简介 视频
- 如果您有其他问题，请在您的 账户状况 控制面板上提交请求。
- 亚马逊商品安全与合规性
- 受影响的商品
- 详情
- Adventskalender 2024 für Kinder Malset,Malset 24 Stück Bastelset Weihnachten,24 Tage lang jeden Tag eine andere Form malen,Kreative DIY-Malerei-Geschenke für Jungen und Mädchen zu Weihnachten
- ASIN： B0DD7R3PPG
- 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的法律、法规、标准和亚马逊政策。
-要销售儿童玩具，您必须满足 儿童玩具帮助页面 上列出的要求，并与我们的合作伙伴第三方测试、检验和认证 (TIC) 服务提供商合作，验证您的商品符合这些要求。
-儿童玩具是指供14岁或以下儿童在学习或玩耍时使用的商品。
-亚马逊根据以下标准来确定商品是否为“儿童玩具”：
-商品包装上的年龄分级标明该玩具专供 14 岁或以下儿童使用。
-产品的包装、展示、促销或广告显示该</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:29:07 +0000</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F260" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="inlineStr">
-        <is>
-          <t>96
- Presenta la documentación sobre seguridad del producto para reactivar los listings
- Hola, Weihai EU:
- Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:25:02 +0000</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F261" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
- opnieuw te activeren</t>
-        </is>
-      </c>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
- Hallo Weihai EU,
- Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:15:34 +0000</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F262" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
-        </is>
-      </c>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:12:56 +0000</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F263" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
-        </is>
-      </c>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr">
-        <is>
-          <t>96
- Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:12:34 +0000</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F264" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 3 Jun 2026 19:09:18 +0000</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F265" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
-        </is>
-      </c>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructio</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14130,39 +13189,39 @@
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14186,39 +13245,39 @@
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14240,39 +13299,39 @@
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:59:29 +0000</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14296,39 +13355,39 @@
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 03:24:34 +0000</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-02</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr"/>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14350,39 +13409,39 @@
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 04:57:38 +0000</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-25</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14404,39 +13463,39 @@
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 04:53:34 +0000</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-25</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14460,39 +13519,39 @@
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 04:38:11 +0000</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14516,39 +13575,39 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 03:47:37 +0000</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-18</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14572,39 +13631,39 @@
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
@@ -14620,39 +13679,39 @@
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 03:04:08 +0000</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Action Required: Transparency Barcode Required for Your Products</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello from Amazon Seller Services,
@@ -14668,39 +13727,39 @@
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 08:49:28 +0000</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>"Gao, Mark" &lt;gaomark@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F277" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>亚马逊广告限时激励活动 - Weihai EU</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>Amazon has replaced the attachment in this email with download link.
 Important: This link may contain content that is confidential. Please exercise appropriate caution when sharing.
@@ -14728,39 +13787,39 @@
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:43:31 +0000</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F278" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -14782,39 +13841,39 @@
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B279" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:43:28 +0000</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F279" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -14836,39 +13895,39 @@
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:03:54 +0000</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F280" s="2" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>You have until July 17 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr"/>
-      <c r="H280" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -14877,39 +13936,39 @@
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B281" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:33:42 +0000</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F281" s="2" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr"/>
-      <c r="H281" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -14921,39 +13980,39 @@
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:07:52 +0000</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except media will need to be 75 characters or less, including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -14965,39 +14024,39 @@
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B283" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D283" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:04:50 +0000</t>
         </is>
       </c>
-      <c r="E283" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F283" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -15009,39 +14068,39 @@
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:18:13 +0000</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F284" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr"/>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less, including spaces. A new item highlights feature now provides an additional 125 characters for sharing materials.
@@ -15053,39 +14112,39 @@
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B285" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 14:50:02 +0000</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F285" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>Earn up to €240 per shipment with C2S2 PCP Pallets</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3yyjt/6708104655/h/1UCuxAj2NkD65NTovD-vcIwWERBh1hVRp_O_epQxzho)
 C2S2 PCP Pallet Spring Promotion: Ship More, Save More
@@ -15107,39 +14166,39 @@
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 11:06:34 +0000</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon stranded inventory &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F286" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>Review stranded inventory scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Fix stranded inventory
@@ -15156,39 +14215,39 @@
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B287" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D287" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:46:42 +0000</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F287" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut de matières dangereuses</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr"/>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut de matières dangereuses
@@ -15209,39 +14268,39 @@
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B288" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:07:01 +0000</t>
         </is>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F288" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr"/>
-      <c r="H288" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -15264,39 +14323,39 @@
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B289" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D289" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:06:59 +0000</t>
         </is>
       </c>
-      <c r="E289" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F289" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -15320,39 +14379,39 @@
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B290" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 07:30:07 +0000</t>
         </is>
       </c>
-      <c r="E290" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>transparency-queue &lt;transparency-queue@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F290" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>成功进行 OPR 评估所需采取的措施</t>
         </is>
       </c>
-      <c r="G290" s="2" t="inlineStr"/>
-      <c r="H290" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>尊敬的Transparency(透明计划)客户：
 您好！感谢您在Transparency(透明计划)中注册您的商品。
@@ -15372,92 +14431,6 @@
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B291" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D291" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:46:25 +0000</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F291" s="2" t="inlineStr">
-        <is>
-          <t>提交商品合规文件，以避免商品被移除</t>
-        </is>
-      </c>
-      <c r="G291" s="2" t="inlineStr"/>
-      <c r="H291" s="2" t="inlineStr">
-        <is>
-          <t>96
- 提交商品合规文件，以避免商品被移除
- 尊敬的 Weihai EU：
-您好！
- 由于缺少安全数据表，您的商品有被移除的风险。请在 2026-09-01之前提交所需文件，以继续销售这些商品。您可以在此电子邮件的底部找到您的存在风险的商品示例。
- 为什么会发生这种情况？
- 我们之所以采取此措施，是因为我们在您的目录中发现了需要安全数据表 (SDS) 的危险品。这些文件是法律要求的，提供有关化学品的重要安全信息，包括妥善处理、储存和应急程序。这有助于确保买家、员工及处理这些商品的每一个人的安全。
- 为了确定该问题，我们同时采用了自动化技术和专家评审，最终做出了这一决定。
- 要了解更多信息，请访问我们 有关化学品销售的要求和常见问题 。
- 如何继续销售受影响的商品？
- 为避免商品被移除并继续销售这些商品，请为每个受影响的商品上传安全数据表 (SDS)。点击下方的“查看合规要求”按钮，查看所有受影响的商品。
- 查看合规性要求
- 哪些商品会受到影响？
- 原因
- 存在风险的销售
- Roaxkois Keramik Bemalen Set | Tassen Bemalen Set Enthält Tass...
- ASIN: B0GKPTF1T7
- SKU: WH-MKB-0130-01
- HazardousGoods
- Unknown
- Roaxkois Keramik Bemalen Set | Tassen Bemalen Set Enthält Tass...
- ASIN: B0GKPTF1T7
- SKU: WHMKB0615
- HazardousGoods
- Unknown
- 如果存在错误？
- 如果您确信无需为自己的商品提交文件：
-- 点击“查看合规性要求”。
-- 点击商品旁边的“提交”。
-- 点击“申诉要求”，然后按照提供的说明操作。
- 如果未提交要求的文件，会怎么样？
- 如果您未在 2026-09-01之前提交所需的安全数据表 (SDS)，则受影响的商品将从所有亚马逊商城中移除。除非您提供所需文件，否则您无法在亚马逊上销售这些商品。
- 我们愿意随时为您提供帮助。
- 如果您对此政策有任何疑问，请联系 销售伙伴支持 。
- 谢谢！
- 亚马逊开店服务
- 报告此电子邮件的问题
- 如果您有任何问题，请访问: Seller Central
- 要更改您的电子邮件首选项，请访问： 通知首选项
- 2026 Amazon.com 旗下公司 保留所有权利
- Amazon EU S.à r.l.
-38 avenue John F. Kennedy,
-L-1855 Luxembourg,
-注册于卢森堡，
-注册编号 B-101818，
-股本 165.833 欧元，
-营业执照编号： 134248，
-卢森堡增值税注册编号 LU 20260743。
- SPC-EUAmazon-686096</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
